--- a/Team-Data/2007-08/12-3-2007-08.xlsx
+++ b/Team-Data/2007-08/12-3-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,67 +728,67 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
         <v>9</v>
       </c>
       <c r="G2" t="n">
-        <v>0.438</v>
+        <v>0.4</v>
       </c>
       <c r="H2" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I2" t="n">
-        <v>34.6</v>
+        <v>34.4</v>
       </c>
       <c r="J2" t="n">
-        <v>77.8</v>
+        <v>77.5</v>
       </c>
       <c r="K2" t="n">
         <v>0.444</v>
       </c>
       <c r="L2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="M2" t="n">
-        <v>13.9</v>
+        <v>13.7</v>
       </c>
       <c r="N2" t="n">
-        <v>0.309</v>
+        <v>0.32</v>
       </c>
       <c r="O2" t="n">
-        <v>20</v>
+        <v>20.6</v>
       </c>
       <c r="P2" t="n">
-        <v>26.3</v>
+        <v>27.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.76</v>
+        <v>0.761</v>
       </c>
       <c r="R2" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="S2" t="n">
-        <v>28.8</v>
+        <v>28.6</v>
       </c>
       <c r="T2" t="n">
         <v>40.9</v>
       </c>
       <c r="U2" t="n">
-        <v>19.6</v>
+        <v>19.1</v>
       </c>
       <c r="V2" t="n">
-        <v>15.9</v>
+        <v>16.1</v>
       </c>
       <c r="W2" t="n">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="X2" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Y2" t="n">
         <v>5.8</v>
@@ -730,19 +797,19 @@
         <v>20.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>93.40000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>-1.4</v>
+        <v>-2.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AE2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF2" t="n">
         <v>14</v>
@@ -754,64 +821,64 @@
         <v>1</v>
       </c>
       <c r="AI2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AJ2" t="n">
         <v>26</v>
       </c>
       <c r="AK2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL2" t="n">
         <v>28</v>
       </c>
       <c r="AM2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AN2" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AO2" t="n">
         <v>12</v>
       </c>
       <c r="AP2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AQ2" t="n">
         <v>13</v>
       </c>
       <c r="AR2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AX2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AZ2" t="n">
         <v>8</v>
       </c>
       <c r="BA2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BB2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC2" t="n">
         <v>17</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-3-2007-08</t>
+          <t>2007-12-03</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>13.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AE3" t="n">
         <v>3</v>
@@ -933,7 +1000,7 @@
         <v>1</v>
       </c>
       <c r="AH3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI3" t="n">
         <v>20</v>
@@ -969,13 +1036,13 @@
         <v>2</v>
       </c>
       <c r="AT3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU3" t="n">
         <v>4</v>
       </c>
       <c r="AV3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AW3" t="n">
         <v>3</v>
@@ -990,7 +1057,7 @@
         <v>20</v>
       </c>
       <c r="BA3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB3" t="n">
         <v>12</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-3-2007-08</t>
+          <t>2007-12-03</t>
         </is>
       </c>
     </row>
@@ -1025,61 +1092,61 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
         <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4" t="n">
-        <v>0.375</v>
+        <v>0.4</v>
       </c>
       <c r="H4" t="n">
         <v>48.3</v>
       </c>
       <c r="I4" t="n">
-        <v>34.3</v>
+        <v>34.8</v>
       </c>
       <c r="J4" t="n">
-        <v>79.3</v>
+        <v>79.2</v>
       </c>
       <c r="K4" t="n">
-        <v>0.433</v>
+        <v>0.439</v>
       </c>
       <c r="L4" t="n">
         <v>6.4</v>
       </c>
       <c r="M4" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="O4" t="n">
         <v>17.3</v>
       </c>
-      <c r="N4" t="n">
-        <v>0.373</v>
-      </c>
-      <c r="O4" t="n">
-        <v>17.4</v>
-      </c>
       <c r="P4" t="n">
-        <v>25.4</v>
+        <v>25.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.674</v>
       </c>
       <c r="R4" t="n">
         <v>12.9</v>
       </c>
       <c r="S4" t="n">
-        <v>28.4</v>
+        <v>28.8</v>
       </c>
       <c r="T4" t="n">
-        <v>41.3</v>
+        <v>41.7</v>
       </c>
       <c r="U4" t="n">
-        <v>19.4</v>
+        <v>19.6</v>
       </c>
       <c r="V4" t="n">
-        <v>16.7</v>
+        <v>17.1</v>
       </c>
       <c r="W4" t="n">
         <v>7.8</v>
@@ -1088,49 +1155,49 @@
         <v>4.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>23.2</v>
+        <v>23.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB4" t="n">
-        <v>92.40000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>-5.8</v>
+        <v>-4.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AE4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AG4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AH4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AJ4" t="n">
         <v>22</v>
       </c>
       <c r="AK4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL4" t="n">
         <v>13</v>
       </c>
       <c r="AM4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN4" t="n">
         <v>6</v>
@@ -1139,46 +1206,46 @@
         <v>20</v>
       </c>
       <c r="AP4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AQ4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AR4" t="n">
         <v>3</v>
       </c>
       <c r="AS4" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AT4" t="n">
         <v>20</v>
       </c>
       <c r="AU4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV4" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AW4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY4" t="n">
         <v>30</v>
       </c>
       <c r="AZ4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BA4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-3-2007-08</t>
+          <t>2007-12-03</t>
         </is>
       </c>
     </row>
@@ -1207,100 +1274,100 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
         <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>0.267</v>
+        <v>0.286</v>
       </c>
       <c r="H5" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I5" t="n">
-        <v>33.8</v>
+        <v>34.1</v>
       </c>
       <c r="J5" t="n">
         <v>85.90000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.393</v>
+        <v>0.397</v>
       </c>
       <c r="L5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="M5" t="n">
         <v>16.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0.312</v>
+        <v>0.303</v>
       </c>
       <c r="O5" t="n">
-        <v>16.3</v>
+        <v>15.3</v>
       </c>
       <c r="P5" t="n">
-        <v>22.2</v>
+        <v>21.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.736</v>
+        <v>0.716</v>
       </c>
       <c r="R5" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="S5" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="T5" t="n">
         <v>44.4</v>
       </c>
       <c r="U5" t="n">
-        <v>20.1</v>
+        <v>20.4</v>
       </c>
       <c r="V5" t="n">
-        <v>15.9</v>
+        <v>16.4</v>
       </c>
       <c r="W5" t="n">
         <v>8.1</v>
       </c>
       <c r="X5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="Z5" t="n">
         <v>21.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.7</v>
+        <v>21.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>89.09999999999999</v>
+        <v>88.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>-6.5</v>
+        <v>-6.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AE5" t="n">
         <v>27</v>
       </c>
       <c r="AF5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG5" t="n">
         <v>27</v>
       </c>
       <c r="AH5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AI5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ5" t="n">
         <v>4</v>
@@ -1309,52 +1376,52 @@
         <v>30</v>
       </c>
       <c r="AL5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM5" t="n">
         <v>18</v>
       </c>
       <c r="AN5" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP5" t="n">
         <v>26</v>
       </c>
-      <c r="AO5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP5" t="n">
+      <c r="AQ5" t="n">
         <v>24</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>18</v>
       </c>
       <c r="AR5" t="n">
         <v>1</v>
       </c>
       <c r="AS5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT5" t="n">
         <v>5</v>
       </c>
       <c r="AU5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV5" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AW5" t="n">
         <v>7</v>
       </c>
       <c r="AX5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY5" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AZ5" t="n">
         <v>16</v>
       </c>
       <c r="BA5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BB5" t="n">
         <v>30</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-3-2007-08</t>
+          <t>2007-12-03</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1537,7 @@
         <v>2</v>
       </c>
       <c r="AE6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF6" t="n">
         <v>14</v>
@@ -1479,7 +1546,7 @@
         <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI6" t="n">
         <v>18</v>
@@ -1488,7 +1555,7 @@
         <v>8</v>
       </c>
       <c r="AK6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL6" t="n">
         <v>10</v>
@@ -1497,22 +1564,22 @@
         <v>10</v>
       </c>
       <c r="AN6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO6" t="n">
         <v>19</v>
       </c>
       <c r="AP6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ6" t="n">
         <v>26</v>
       </c>
       <c r="AR6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT6" t="n">
         <v>7</v>
@@ -1521,7 +1588,7 @@
         <v>26</v>
       </c>
       <c r="AV6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW6" t="n">
         <v>18</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-3-2007-08</t>
+          <t>2007-12-03</t>
         </is>
       </c>
     </row>
@@ -1571,103 +1638,103 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.667</v>
+        <v>0.647</v>
       </c>
       <c r="H7" t="n">
         <v>48.3</v>
       </c>
       <c r="I7" t="n">
-        <v>36.9</v>
+        <v>37</v>
       </c>
       <c r="J7" t="n">
-        <v>79.8</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.463</v>
+        <v>0.462</v>
       </c>
       <c r="L7" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="M7" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="N7" t="n">
-        <v>0.331</v>
+        <v>0.329</v>
       </c>
       <c r="O7" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="P7" t="n">
-        <v>27.2</v>
+        <v>27.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.845</v>
+        <v>0.839</v>
       </c>
       <c r="R7" t="n">
-        <v>10.3</v>
+        <v>10.6</v>
       </c>
       <c r="S7" t="n">
-        <v>32.1</v>
+        <v>31.9</v>
       </c>
       <c r="T7" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="U7" t="n">
         <v>20.6</v>
       </c>
       <c r="V7" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="W7" t="n">
         <v>5.7</v>
       </c>
       <c r="X7" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="AA7" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>102.6</v>
+        <v>102.5</v>
       </c>
       <c r="AC7" t="n">
         <v>4.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AE7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF7" t="n">
         <v>7</v>
       </c>
       <c r="AG7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK7" t="n">
         <v>10</v>
@@ -1676,28 +1743,28 @@
         <v>19</v>
       </c>
       <c r="AM7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN7" t="n">
         <v>23</v>
       </c>
       <c r="AO7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR7" t="n">
         <v>19</v>
       </c>
       <c r="AS7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AT7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU7" t="n">
         <v>15</v>
@@ -1709,13 +1776,13 @@
         <v>30</v>
       </c>
       <c r="AX7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AY7" t="n">
         <v>7</v>
       </c>
       <c r="AZ7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA7" t="n">
         <v>12</v>
@@ -1724,7 +1791,7 @@
         <v>8</v>
       </c>
       <c r="BC7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-3-2007-08</t>
+          <t>2007-12-03</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1901,7 @@
         <v>2</v>
       </c>
       <c r="AE8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF8" t="n">
         <v>9</v>
@@ -1858,10 +1925,10 @@
         <v>11</v>
       </c>
       <c r="AM8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO8" t="n">
         <v>5</v>
@@ -1885,13 +1952,13 @@
         <v>5</v>
       </c>
       <c r="AV8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
       </c>
       <c r="AX8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-3-2007-08</t>
+          <t>2007-12-03</t>
         </is>
       </c>
     </row>
@@ -2013,10 +2080,10 @@
         <v>8</v>
       </c>
       <c r="AD9" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AE9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF9" t="n">
         <v>5</v>
@@ -2037,19 +2104,19 @@
         <v>5</v>
       </c>
       <c r="AL9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AM9" t="n">
         <v>21</v>
       </c>
       <c r="AN9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AO9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ9" t="n">
         <v>21</v>
@@ -2073,7 +2140,7 @@
         <v>20</v>
       </c>
       <c r="AX9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY9" t="n">
         <v>1</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-3-2007-08</t>
+          <t>2007-12-03</t>
         </is>
       </c>
     </row>
@@ -2117,97 +2184,97 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E10" t="n">
         <v>9</v>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>0.529</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>48.6</v>
+        <v>48.3</v>
       </c>
       <c r="I10" t="n">
         <v>40.6</v>
       </c>
       <c r="J10" t="n">
-        <v>90.40000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.45</v>
+        <v>0.455</v>
       </c>
       <c r="L10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>27.2</v>
+        <v>26.4</v>
       </c>
       <c r="N10" t="n">
-        <v>0.339</v>
+        <v>0.35</v>
       </c>
       <c r="O10" t="n">
-        <v>18.6</v>
+        <v>18.3</v>
       </c>
       <c r="P10" t="n">
-        <v>26.8</v>
+        <v>26.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="R10" t="n">
-        <v>12.4</v>
+        <v>12.1</v>
       </c>
       <c r="S10" t="n">
-        <v>30.8</v>
+        <v>30.4</v>
       </c>
       <c r="T10" t="n">
-        <v>43.2</v>
+        <v>42.5</v>
       </c>
       <c r="U10" t="n">
-        <v>22.5</v>
+        <v>22.2</v>
       </c>
       <c r="V10" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="W10" t="n">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>109.1</v>
+        <v>108.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="AD10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH10" t="n">
         <v>13</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>5</v>
       </c>
       <c r="AI10" t="n">
         <v>2</v>
@@ -2216,61 +2283,61 @@
         <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AL10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM10" t="n">
         <v>1</v>
       </c>
       <c r="AN10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AO10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP10" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AQ10" t="n">
         <v>28</v>
       </c>
       <c r="AR10" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AS10" t="n">
         <v>17</v>
       </c>
       <c r="AT10" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AU10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA10" t="n">
         <v>9</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>26</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>8</v>
       </c>
       <c r="BB10" t="n">
         <v>1</v>
       </c>
       <c r="BC10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-3-2007-08</t>
+          <t>2007-12-03</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2447,7 @@
         <v>2</v>
       </c>
       <c r="AE11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF11" t="n">
         <v>14</v>
@@ -2416,19 +2483,19 @@
         <v>23</v>
       </c>
       <c r="AQ11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR11" t="n">
         <v>6</v>
       </c>
       <c r="AS11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT11" t="n">
         <v>4</v>
       </c>
       <c r="AU11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV11" t="n">
         <v>7</v>
@@ -2437,13 +2504,13 @@
         <v>14</v>
       </c>
       <c r="AX11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY11" t="n">
         <v>11</v>
       </c>
       <c r="AZ11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA11" t="n">
         <v>24</v>
@@ -2452,7 +2519,7 @@
         <v>19</v>
       </c>
       <c r="BC11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-3-2007-08</t>
+          <t>2007-12-03</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2629,7 @@
         <v>2</v>
       </c>
       <c r="AE12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF12" t="n">
         <v>14</v>
@@ -2571,7 +2638,7 @@
         <v>13</v>
       </c>
       <c r="AH12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI12" t="n">
         <v>10</v>
@@ -2610,19 +2677,19 @@
         <v>1</v>
       </c>
       <c r="AU12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AW12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX12" t="n">
         <v>4</v>
       </c>
       <c r="AY12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ12" t="n">
         <v>30</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-3-2007-08</t>
+          <t>2007-12-03</t>
         </is>
       </c>
     </row>
@@ -2741,16 +2808,16 @@
         <v>-5.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF13" t="n">
         <v>14</v>
       </c>
       <c r="AG13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH13" t="n">
         <v>19</v>
@@ -2792,7 +2859,7 @@
         <v>11</v>
       </c>
       <c r="AU13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV13" t="n">
         <v>17</v>
@@ -2801,7 +2868,7 @@
         <v>27</v>
       </c>
       <c r="AX13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY13" t="n">
         <v>21</v>
@@ -2816,7 +2883,7 @@
         <v>21</v>
       </c>
       <c r="BC13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-3-2007-08</t>
+          <t>2007-12-03</t>
         </is>
       </c>
     </row>
@@ -2923,13 +2990,13 @@
         <v>3.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF14" t="n">
         <v>11</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>10</v>
       </c>
       <c r="AG14" t="n">
         <v>11</v>
@@ -2953,7 +3020,7 @@
         <v>12</v>
       </c>
       <c r="AN14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO14" t="n">
         <v>2</v>
@@ -2977,13 +3044,13 @@
         <v>8</v>
       </c>
       <c r="AV14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY14" t="n">
         <v>17</v>
@@ -2992,7 +3059,7 @@
         <v>17</v>
       </c>
       <c r="BA14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB14" t="n">
         <v>5</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-3-2007-08</t>
+          <t>2007-12-03</t>
         </is>
       </c>
     </row>
@@ -3027,64 +3094,64 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E15" t="n">
         <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G15" t="n">
-        <v>0.353</v>
+        <v>0.375</v>
       </c>
       <c r="H15" t="n">
         <v>48.3</v>
       </c>
       <c r="I15" t="n">
-        <v>37.6</v>
+        <v>37.4</v>
       </c>
       <c r="J15" t="n">
-        <v>80.7</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K15" t="n">
         <v>0.466</v>
       </c>
       <c r="L15" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="M15" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="N15" t="n">
-        <v>0.409</v>
+        <v>0.401</v>
       </c>
       <c r="O15" t="n">
-        <v>20.5</v>
+        <v>21.1</v>
       </c>
       <c r="P15" t="n">
-        <v>26.8</v>
+        <v>27.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.765</v>
+        <v>0.762</v>
       </c>
       <c r="R15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="S15" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="T15" t="n">
         <v>42.1</v>
       </c>
       <c r="U15" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="V15" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="W15" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="X15" t="n">
         <v>5.4</v>
@@ -3093,10 +3160,10 @@
         <v>4.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.2</v>
+        <v>19.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>23.1</v>
+        <v>23.6</v>
       </c>
       <c r="AB15" t="n">
         <v>104.5</v>
@@ -3105,22 +3172,22 @@
         <v>-1</v>
       </c>
       <c r="AD15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH15" t="n">
         <v>13</v>
       </c>
-      <c r="AE15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>15</v>
-      </c>
       <c r="AI15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ15" t="n">
         <v>16</v>
@@ -3129,7 +3196,7 @@
         <v>7</v>
       </c>
       <c r="AL15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AM15" t="n">
         <v>5</v>
@@ -3138,13 +3205,13 @@
         <v>3</v>
       </c>
       <c r="AO15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ15" t="n">
         <v>11</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>9</v>
       </c>
       <c r="AR15" t="n">
         <v>24</v>
@@ -3153,7 +3220,7 @@
         <v>9</v>
       </c>
       <c r="AT15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU15" t="n">
         <v>13</v>
@@ -3165,16 +3232,16 @@
         <v>29</v>
       </c>
       <c r="AX15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AY15" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BA15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BB15" t="n">
         <v>6</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-3-2007-08</t>
+          <t>2007-12-03</t>
         </is>
       </c>
     </row>
@@ -3209,91 +3276,91 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E16" t="n">
         <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G16" t="n">
-        <v>0.235</v>
+        <v>0.25</v>
       </c>
       <c r="H16" t="n">
         <v>48</v>
       </c>
       <c r="I16" t="n">
-        <v>33.9</v>
+        <v>33.5</v>
       </c>
       <c r="J16" t="n">
-        <v>75.7</v>
+        <v>75.8</v>
       </c>
       <c r="K16" t="n">
-        <v>0.448</v>
+        <v>0.442</v>
       </c>
       <c r="L16" t="n">
         <v>4.9</v>
       </c>
       <c r="M16" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="N16" t="n">
-        <v>0.333</v>
+        <v>0.329</v>
       </c>
       <c r="O16" t="n">
         <v>16.8</v>
       </c>
       <c r="P16" t="n">
-        <v>24.9</v>
+        <v>24.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.674</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="R16" t="n">
         <v>8.5</v>
       </c>
       <c r="S16" t="n">
-        <v>30</v>
+        <v>30.4</v>
       </c>
       <c r="T16" t="n">
-        <v>38.5</v>
+        <v>38.9</v>
       </c>
       <c r="U16" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="V16" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="W16" t="n">
         <v>7.9</v>
       </c>
       <c r="X16" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>89.5</v>
+        <v>88.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>-5.3</v>
+        <v>-5.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE16" t="n">
         <v>27</v>
       </c>
       <c r="AF16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG16" t="n">
         <v>28</v>
@@ -3302,13 +3369,13 @@
         <v>19</v>
       </c>
       <c r="AI16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ16" t="n">
         <v>29</v>
       </c>
       <c r="AK16" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AL16" t="n">
         <v>24</v>
@@ -3326,13 +3393,13 @@
         <v>21</v>
       </c>
       <c r="AQ16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AR16" t="n">
         <v>29</v>
       </c>
       <c r="AS16" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AT16" t="n">
         <v>30</v>
@@ -3341,28 +3408,28 @@
         <v>27</v>
       </c>
       <c r="AV16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AW16" t="n">
         <v>8</v>
       </c>
       <c r="AX16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AY16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB16" t="n">
         <v>29</v>
       </c>
       <c r="BC16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-3-2007-08</t>
+          <t>2007-12-03</t>
         </is>
       </c>
     </row>
@@ -3469,13 +3536,13 @@
         <v>-4.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE17" t="n">
         <v>18</v>
       </c>
       <c r="AF17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG17" t="n">
         <v>18</v>
@@ -3484,7 +3551,7 @@
         <v>19</v>
       </c>
       <c r="AI17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ17" t="n">
         <v>24</v>
@@ -3508,7 +3575,7 @@
         <v>22</v>
       </c>
       <c r="AQ17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR17" t="n">
         <v>15</v>
@@ -3529,13 +3596,13 @@
         <v>26</v>
       </c>
       <c r="AX17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA17" t="n">
         <v>14</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-3-2007-08</t>
+          <t>2007-12-03</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3718,13 @@
         <v>-9</v>
       </c>
       <c r="AD18" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
       </c>
       <c r="AF18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG18" t="n">
         <v>30</v>
@@ -3672,7 +3739,7 @@
         <v>12</v>
       </c>
       <c r="AK18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL18" t="n">
         <v>16</v>
@@ -3681,7 +3748,7 @@
         <v>19</v>
       </c>
       <c r="AN18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO18" t="n">
         <v>30</v>
@@ -3690,13 +3757,13 @@
         <v>29</v>
       </c>
       <c r="AQ18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR18" t="n">
         <v>11</v>
       </c>
       <c r="AS18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT18" t="n">
         <v>25</v>
@@ -3705,13 +3772,13 @@
         <v>28</v>
       </c>
       <c r="AV18" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AW18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY18" t="n">
         <v>13</v>
@@ -3723,7 +3790,7 @@
         <v>29</v>
       </c>
       <c r="BB18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC18" t="n">
         <v>30</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-3-2007-08</t>
+          <t>2007-12-03</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-7.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE19" t="n">
         <v>16</v>
@@ -3845,7 +3912,7 @@
         <v>16</v>
       </c>
       <c r="AH19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI19" t="n">
         <v>30</v>
@@ -3857,7 +3924,7 @@
         <v>29</v>
       </c>
       <c r="AL19" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AM19" t="n">
         <v>14</v>
@@ -3869,13 +3936,13 @@
         <v>7</v>
       </c>
       <c r="AP19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ19" t="n">
         <v>15</v>
       </c>
       <c r="AR19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS19" t="n">
         <v>21</v>
@@ -3887,13 +3954,13 @@
         <v>9</v>
       </c>
       <c r="AV19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AW19" t="n">
         <v>24</v>
       </c>
       <c r="AX19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY19" t="n">
         <v>9</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-3-2007-08</t>
+          <t>2007-12-03</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4085,7 @@
         <v>2</v>
       </c>
       <c r="AE20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF20" t="n">
         <v>7</v>
@@ -4027,7 +4094,7 @@
         <v>7</v>
       </c>
       <c r="AH20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI20" t="n">
         <v>18</v>
@@ -4036,13 +4103,13 @@
         <v>11</v>
       </c>
       <c r="AK20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL20" t="n">
         <v>7</v>
       </c>
       <c r="AM20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN20" t="n">
         <v>5</v>
@@ -4063,13 +4130,13 @@
         <v>13</v>
       </c>
       <c r="AT20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW20" t="n">
         <v>13</v>
@@ -4081,7 +4148,7 @@
         <v>4</v>
       </c>
       <c r="AZ20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA20" t="n">
         <v>27</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-3-2007-08</t>
+          <t>2007-12-03</t>
         </is>
       </c>
     </row>
@@ -4197,22 +4264,22 @@
         <v>-8.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AE21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF21" t="n">
         <v>25</v>
       </c>
-      <c r="AF21" t="n">
-        <v>23</v>
-      </c>
       <c r="AG21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ21" t="n">
         <v>13</v>
@@ -4221,19 +4288,19 @@
         <v>27</v>
       </c>
       <c r="AL21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AN21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO21" t="n">
         <v>15</v>
       </c>
       <c r="AP21" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ21" t="n">
         <v>27</v>
@@ -4245,7 +4312,7 @@
         <v>19</v>
       </c>
       <c r="AT21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU21" t="n">
         <v>29</v>
@@ -4269,7 +4336,7 @@
         <v>11</v>
       </c>
       <c r="BB21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC21" t="n">
         <v>28</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-3-2007-08</t>
+          <t>2007-12-03</t>
         </is>
       </c>
     </row>
@@ -4301,79 +4368,79 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F22" t="n">
         <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8</v>
+        <v>0.789</v>
       </c>
       <c r="H22" t="n">
-        <v>48.5</v>
+        <v>48.3</v>
       </c>
       <c r="I22" t="n">
-        <v>37.2</v>
+        <v>36.7</v>
       </c>
       <c r="J22" t="n">
-        <v>79.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>0.466</v>
+        <v>0.465</v>
       </c>
       <c r="L22" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M22" t="n">
         <v>26.1</v>
       </c>
       <c r="N22" t="n">
-        <v>0.355</v>
+        <v>0.351</v>
       </c>
       <c r="O22" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="P22" t="n">
-        <v>29.1</v>
+        <v>28.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.719</v>
+        <v>0.721</v>
       </c>
       <c r="R22" t="n">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>35.4</v>
+        <v>35.1</v>
       </c>
       <c r="T22" t="n">
-        <v>44.3</v>
+        <v>43.8</v>
       </c>
       <c r="U22" t="n">
-        <v>21.9</v>
+        <v>21.5</v>
       </c>
       <c r="V22" t="n">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="W22" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="X22" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="Y22" t="n">
         <v>4.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.1</v>
+        <v>19.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>104.5</v>
+        <v>103.5</v>
       </c>
       <c r="AC22" t="n">
         <v>6.9</v>
@@ -4391,19 +4458,19 @@
         <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AI22" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AJ22" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AK22" t="n">
         <v>8</v>
       </c>
       <c r="AL22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM22" t="n">
         <v>2</v>
@@ -4412,13 +4479,13 @@
         <v>14</v>
       </c>
       <c r="AO22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR22" t="n">
         <v>28</v>
@@ -4439,13 +4506,13 @@
         <v>25</v>
       </c>
       <c r="AX22" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AY22" t="n">
         <v>6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA22" t="n">
         <v>5</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-3-2007-08</t>
+          <t>2007-12-03</t>
         </is>
       </c>
     </row>
@@ -4483,64 +4550,64 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E23" t="n">
         <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G23" t="n">
-        <v>0.294</v>
+        <v>0.313</v>
       </c>
       <c r="H23" t="n">
         <v>48.6</v>
       </c>
       <c r="I23" t="n">
-        <v>34.4</v>
+        <v>34.6</v>
       </c>
       <c r="J23" t="n">
-        <v>79.3</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.433</v>
+        <v>0.435</v>
       </c>
       <c r="L23" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="M23" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="N23" t="n">
-        <v>0.302</v>
+        <v>0.308</v>
       </c>
       <c r="O23" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="P23" t="n">
         <v>25.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.704</v>
+        <v>0.706</v>
       </c>
       <c r="R23" t="n">
-        <v>13.2</v>
+        <v>13.5</v>
       </c>
       <c r="S23" t="n">
-        <v>30.4</v>
+        <v>30</v>
       </c>
       <c r="T23" t="n">
         <v>43.5</v>
       </c>
       <c r="U23" t="n">
-        <v>20</v>
+        <v>20.4</v>
       </c>
       <c r="V23" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="W23" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X23" t="n">
         <v>5.3</v>
@@ -4549,55 +4616,55 @@
         <v>4.8</v>
       </c>
       <c r="Z23" t="n">
-        <v>21.4</v>
+        <v>21.7</v>
       </c>
       <c r="AA23" t="n">
         <v>20.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>90.8</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>-3.1</v>
+        <v>-2.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF23" t="n">
         <v>25</v>
       </c>
-      <c r="AF23" t="n">
-        <v>26</v>
-      </c>
       <c r="AG23" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AH23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AI23" t="n">
         <v>25</v>
       </c>
       <c r="AJ23" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AK23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL23" t="n">
         <v>29</v>
       </c>
       <c r="AM23" t="n">
+        <v>27</v>
+      </c>
+      <c r="AN23" t="n">
         <v>28</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>30</v>
       </c>
       <c r="AO23" t="n">
         <v>18</v>
       </c>
       <c r="AP23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ23" t="n">
         <v>25</v>
@@ -4606,34 +4673,34 @@
         <v>2</v>
       </c>
       <c r="AS23" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AT23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU23" t="n">
+        <v>17</v>
+      </c>
+      <c r="AV23" t="n">
         <v>22</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>24</v>
       </c>
       <c r="AW23" t="n">
         <v>19</v>
       </c>
       <c r="AX23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY23" t="n">
         <v>14</v>
       </c>
       <c r="AZ23" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA23" t="n">
         <v>23</v>
       </c>
       <c r="BB23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC23" t="n">
         <v>18</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-3-2007-08</t>
+          <t>2007-12-03</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>5.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE24" t="n">
         <v>4</v>
@@ -4767,7 +4834,7 @@
         <v>2</v>
       </c>
       <c r="AL24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM24" t="n">
         <v>3</v>
@@ -4779,7 +4846,7 @@
         <v>22</v>
       </c>
       <c r="AP24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ24" t="n">
         <v>8</v>
@@ -4791,7 +4858,7 @@
         <v>5</v>
       </c>
       <c r="AT24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU24" t="n">
         <v>2</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-3-2007-08</t>
+          <t>2007-12-03</t>
         </is>
       </c>
     </row>
@@ -4847,124 +4914,124 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F25" t="n">
         <v>12</v>
       </c>
       <c r="G25" t="n">
-        <v>0.333</v>
+        <v>0.294</v>
       </c>
       <c r="H25" t="n">
         <v>48</v>
       </c>
       <c r="I25" t="n">
-        <v>35.1</v>
+        <v>34.6</v>
       </c>
       <c r="J25" t="n">
-        <v>77.40000000000001</v>
+        <v>77</v>
       </c>
       <c r="K25" t="n">
-        <v>0.454</v>
+        <v>0.45</v>
       </c>
       <c r="L25" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="M25" t="n">
-        <v>15.6</v>
+        <v>15.2</v>
       </c>
       <c r="N25" t="n">
-        <v>0.37</v>
+        <v>0.355</v>
       </c>
       <c r="O25" t="n">
-        <v>15.4</v>
+        <v>15.8</v>
       </c>
       <c r="P25" t="n">
-        <v>21.2</v>
+        <v>21.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.725</v>
+        <v>0.727</v>
       </c>
       <c r="R25" t="n">
         <v>9.5</v>
       </c>
       <c r="S25" t="n">
-        <v>29.4</v>
+        <v>29.5</v>
       </c>
       <c r="T25" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="U25" t="n">
-        <v>20.3</v>
+        <v>20</v>
       </c>
       <c r="V25" t="n">
-        <v>15.3</v>
+        <v>15.5</v>
       </c>
       <c r="W25" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="X25" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y25" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.5</v>
+        <v>20.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>20.9</v>
+        <v>21.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>91.40000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>-5.8</v>
+        <v>-6.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AE25" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AF25" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG25" t="n">
         <v>26</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>24</v>
       </c>
       <c r="AH25" t="n">
         <v>19</v>
       </c>
       <c r="AI25" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AJ25" t="n">
         <v>27</v>
       </c>
       <c r="AK25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>24</v>
+      </c>
+      <c r="AN25" t="n">
         <v>12</v>
       </c>
-      <c r="AL25" t="n">
-        <v>18</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>22</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>9</v>
-      </c>
       <c r="AO25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP25" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AQ25" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AR25" t="n">
         <v>25</v>
@@ -4976,10 +5043,10 @@
         <v>29</v>
       </c>
       <c r="AU25" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AV25" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AW25" t="n">
         <v>28</v>
@@ -4988,16 +5055,16 @@
         <v>25</v>
       </c>
       <c r="AY25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ25" t="n">
         <v>9</v>
       </c>
       <c r="BA25" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BB25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC25" t="n">
         <v>25</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-3-2007-08</t>
+          <t>2007-12-03</t>
         </is>
       </c>
     </row>
@@ -5107,19 +5174,19 @@
         <v>-3.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AE26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI26" t="n">
         <v>21</v>
@@ -5128,13 +5195,13 @@
         <v>25</v>
       </c>
       <c r="AK26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AM26" t="n">
         <v>23</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>24</v>
       </c>
       <c r="AN26" t="n">
         <v>21</v>
@@ -5149,7 +5216,7 @@
         <v>3</v>
       </c>
       <c r="AR26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS26" t="n">
         <v>24</v>
@@ -5161,7 +5228,7 @@
         <v>30</v>
       </c>
       <c r="AV26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW26" t="n">
         <v>17</v>
@@ -5170,7 +5237,7 @@
         <v>29</v>
       </c>
       <c r="AY26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ26" t="n">
         <v>18</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-3-2007-08</t>
+          <t>2007-12-03</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5359,7 @@
         <v>2</v>
       </c>
       <c r="AE27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF27" t="n">
         <v>2</v>
@@ -5307,7 +5374,7 @@
         <v>4</v>
       </c>
       <c r="AJ27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK27" t="n">
         <v>3</v>
@@ -5316,19 +5383,19 @@
         <v>6</v>
       </c>
       <c r="AM27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AN27" t="n">
         <v>2</v>
       </c>
       <c r="AO27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP27" t="n">
         <v>27</v>
       </c>
       <c r="AQ27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR27" t="n">
         <v>26</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-3-2007-08</t>
+          <t>2007-12-03</t>
         </is>
       </c>
     </row>
@@ -5483,10 +5550,10 @@
         <v>29</v>
       </c>
       <c r="AH28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ28" t="n">
         <v>2</v>
@@ -5501,7 +5568,7 @@
         <v>29</v>
       </c>
       <c r="AN28" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AO28" t="n">
         <v>14</v>
@@ -5510,7 +5577,7 @@
         <v>20</v>
       </c>
       <c r="AQ28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR28" t="n">
         <v>14</v>
@@ -5537,10 +5604,10 @@
         <v>19</v>
       </c>
       <c r="AZ28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA28" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BB28" t="n">
         <v>15</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-3-2007-08</t>
+          <t>2007-12-03</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F29" t="n">
         <v>8</v>
       </c>
       <c r="G29" t="n">
-        <v>0.556</v>
+        <v>0.529</v>
       </c>
       <c r="H29" t="n">
         <v>48.3</v>
@@ -5593,46 +5660,46 @@
         <v>37.3</v>
       </c>
       <c r="J29" t="n">
-        <v>83</v>
+        <v>83.5</v>
       </c>
       <c r="K29" t="n">
-        <v>0.45</v>
+        <v>0.447</v>
       </c>
       <c r="L29" t="n">
         <v>8.6</v>
       </c>
       <c r="M29" t="n">
-        <v>19.9</v>
+        <v>20.3</v>
       </c>
       <c r="N29" t="n">
-        <v>0.433</v>
+        <v>0.426</v>
       </c>
       <c r="O29" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="P29" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.839</v>
+        <v>0.843</v>
       </c>
       <c r="R29" t="n">
-        <v>10.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S29" t="n">
         <v>31.1</v>
       </c>
       <c r="T29" t="n">
-        <v>41.2</v>
+        <v>40.9</v>
       </c>
       <c r="U29" t="n">
         <v>23.2</v>
       </c>
       <c r="V29" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="W29" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="X29" t="n">
         <v>3.9</v>
@@ -5641,31 +5708,31 @@
         <v>4.8</v>
       </c>
       <c r="Z29" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="AB29" t="n">
         <v>98.7</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AE29" t="n">
         <v>10</v>
       </c>
       <c r="AF29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI29" t="n">
         <v>11</v>
@@ -5674,13 +5741,13 @@
         <v>7</v>
       </c>
       <c r="AK29" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AL29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AM29" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AN29" t="n">
         <v>1</v>
@@ -5692,16 +5759,16 @@
         <v>30</v>
       </c>
       <c r="AQ29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR29" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AS29" t="n">
         <v>16</v>
       </c>
       <c r="AT29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU29" t="n">
         <v>6</v>
@@ -5716,7 +5783,7 @@
         <v>27</v>
       </c>
       <c r="AY29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ29" t="n">
         <v>10</v>
@@ -5728,7 +5795,7 @@
         <v>16</v>
       </c>
       <c r="BC29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-3-2007-08</t>
+          <t>2007-12-03</t>
         </is>
       </c>
     </row>
@@ -5757,88 +5824,88 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F30" t="n">
         <v>5</v>
       </c>
       <c r="G30" t="n">
-        <v>0.722</v>
+        <v>0.706</v>
       </c>
       <c r="H30" t="n">
         <v>48</v>
       </c>
       <c r="I30" t="n">
-        <v>40.1</v>
+        <v>39.9</v>
       </c>
       <c r="J30" t="n">
-        <v>80.90000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>0.495</v>
+        <v>0.493</v>
       </c>
       <c r="L30" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="M30" t="n">
         <v>11.2</v>
       </c>
       <c r="N30" t="n">
-        <v>0.358</v>
+        <v>0.347</v>
       </c>
       <c r="O30" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="P30" t="n">
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.761</v>
+        <v>0.763</v>
       </c>
       <c r="R30" t="n">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
       <c r="S30" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="T30" t="n">
-        <v>41.9</v>
+        <v>42.2</v>
       </c>
       <c r="U30" t="n">
-        <v>27.2</v>
+        <v>26.6</v>
       </c>
       <c r="V30" t="n">
-        <v>16.2</v>
+        <v>16.4</v>
       </c>
       <c r="W30" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="X30" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y30" t="n">
         <v>5.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="AB30" t="n">
-        <v>107.1</v>
+        <v>106.9</v>
       </c>
       <c r="AC30" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AE30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF30" t="n">
         <v>5</v>
@@ -5865,31 +5932,31 @@
         <v>30</v>
       </c>
       <c r="AN30" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AO30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP30" t="n">
         <v>2</v>
       </c>
       <c r="AQ30" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AR30" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AS30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT30" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AU30" t="n">
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW30" t="n">
         <v>2</v>
@@ -5901,7 +5968,7 @@
         <v>28</v>
       </c>
       <c r="AZ30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA30" t="n">
         <v>4</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-3-2007-08</t>
+          <t>2007-12-03</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-0.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE31" t="n">
         <v>16</v>
@@ -6029,10 +6096,10 @@
         <v>16</v>
       </c>
       <c r="AH31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ31" t="n">
         <v>10</v>
@@ -6050,16 +6117,16 @@
         <v>18</v>
       </c>
       <c r="AO31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP31" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ31" t="n">
         <v>7</v>
       </c>
       <c r="AR31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS31" t="n">
         <v>14</v>
@@ -6071,19 +6138,19 @@
         <v>21</v>
       </c>
       <c r="AV31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW31" t="n">
         <v>16</v>
       </c>
       <c r="AX31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY31" t="n">
         <v>8</v>
       </c>
       <c r="AZ31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA31" t="n">
         <v>13</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-3-2007-08</t>
+          <t>2007-12-03</t>
         </is>
       </c>
     </row>
